--- a/Honda_Logi/Excel_Format/包装仕様一覧.xlsx
+++ b/Honda_Logi/Excel_Format/包装仕様一覧.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4685CF-0D68-40F7-9F22-38EC26F99E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52F1FE2-1505-41F5-8B02-A29D3138A4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29595" yWindow="9000" windowWidth="23040" windowHeight="12735" xr2:uid="{6540BE86-D85E-4ADA-8294-278721967E3B}"/>
+    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{6540BE86-D85E-4ADA-8294-278721967E3B}"/>
   </bookViews>
   <sheets>
     <sheet name="包装仕様一覧" sheetId="1" r:id="rId1"/>
@@ -159,7 +159,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +196,14 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -318,8 +326,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -363,6 +374,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -372,20 +392,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -761,20 +773,19 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.125" style="16" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="13" customWidth="1"/>
     <col min="3" max="4" width="11.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.125" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.625" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="17" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.125" style="16" customWidth="1"/>
-    <col min="10" max="10" width="11.125" style="17" customWidth="1"/>
-    <col min="11" max="11" width="11.125" style="18" customWidth="1"/>
-    <col min="12" max="12" width="11.125" style="19" customWidth="1"/>
-    <col min="13" max="13" width="11.125" style="16" customWidth="1"/>
-    <col min="14" max="15" width="11.125" style="17" customWidth="1"/>
-    <col min="16" max="16" width="11.125" style="16" customWidth="1"/>
-    <col min="17" max="17" width="11.125" style="17" customWidth="1"/>
+    <col min="5" max="5" width="20.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="14" customWidth="1"/>
+    <col min="11" max="12" width="11.125" style="15" customWidth="1"/>
+    <col min="13" max="13" width="11.125" style="13" customWidth="1"/>
+    <col min="14" max="15" width="11.125" style="19" customWidth="1"/>
+    <col min="16" max="16" width="11.125" style="13" customWidth="1"/>
+    <col min="17" max="17" width="11.125" style="14" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -827,12 +838,12 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="15"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="18"/>
       <c r="L3" s="6" t="s">
         <v>3</v>
       </c>

--- a/Honda_Logi/Excel_Format/包装仕様一覧.xlsx
+++ b/Honda_Logi/Excel_Format/包装仕様一覧.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A52F1FE2-1505-41F5-8B02-A29D3138A4B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61403F82-24B6-4DA4-AF38-FCB628405E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{6540BE86-D85E-4ADA-8294-278721967E3B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>DIST：</t>
     <phoneticPr fontId="3"/>
@@ -149,6 +149,10 @@
   </si>
   <si>
     <t>LOT：</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ケースNo</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -383,6 +387,9 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -391,9 +398,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -769,27 +773,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Q4"/>
+  <dimension ref="B1:R4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.125" style="13" customWidth="1"/>
-    <col min="3" max="4" width="11.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="14" customWidth="1"/>
-    <col min="8" max="8" width="13.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.125" style="13" customWidth="1"/>
-    <col min="10" max="10" width="11.125" style="14" customWidth="1"/>
-    <col min="11" max="12" width="11.125" style="15" customWidth="1"/>
-    <col min="13" max="13" width="11.125" style="13" customWidth="1"/>
-    <col min="14" max="15" width="11.125" style="19" customWidth="1"/>
-    <col min="16" max="16" width="11.125" style="13" customWidth="1"/>
-    <col min="17" max="17" width="11.125" style="14" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="2" max="5" width="11.125" style="13" customWidth="1"/>
+    <col min="6" max="6" width="20.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="13" customWidth="1"/>
+    <col min="11" max="11" width="11.125" style="14" customWidth="1"/>
+    <col min="12" max="13" width="11.125" style="15" customWidth="1"/>
+    <col min="14" max="14" width="11.125" style="13" customWidth="1"/>
+    <col min="15" max="16" width="11.125" style="16" customWidth="1"/>
+    <col min="17" max="17" width="11.125" style="13" customWidth="1"/>
+    <col min="18" max="18" width="11.125" style="14" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -806,56 +809,59 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="3"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1"/>
+      <c r="M2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="1"/>
+      <c r="N2" s="3"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="4"/>
+      <c r="I3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
+      <c r="J3" s="18"/>
       <c r="K3" s="18"/>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="19"/>
+      <c r="M3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="8" t="s">
+      <c r="N3" s="6"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="7"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="7"/>
     </row>
-    <row r="4" spans="2:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:18" x14ac:dyDescent="0.4">
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
@@ -866,48 +872,51 @@
         <v>7</v>
       </c>
       <c r="E4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="I4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="L4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="N4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="O4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="P4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="Q4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="R4" s="11" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="I3:L3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
